--- a/artfynd/A 62595-2023 artfynd.xlsx
+++ b/artfynd/A 62595-2023 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 62595-2023 artfynd.xlsx
+++ b/artfynd/A 62595-2023 artfynd.xlsx
@@ -675,15 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>111659789</v>
+        <v>112934773</v>
       </c>
       <c r="B2" t="n">
-        <v>96268</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91872</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -691,19 +686,23 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>223597</v>
+        <v>5447</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Jungfru marie nycklar</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata subsp. maculata</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr"/>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
@@ -711,13 +710,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>776795</v>
+        <v>776809</v>
       </c>
       <c r="R2" t="n">
-        <v>7198204</v>
+        <v>7198215</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -761,12 +760,12 @@
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Julia Scholten</t>
+          <t>Linda Sandberg</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Julia Scholten, Anton Andersson</t>
+          <t>Linda Sandberg</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
@@ -776,16 +775,11 @@
         <v>112934656</v>
       </c>
       <c r="B3" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -880,19 +874,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>112934772</v>
+        <v>112934771</v>
       </c>
       <c r="B4" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -920,10 +909,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>776794</v>
+        <v>776770</v>
       </c>
       <c r="R4" t="n">
-        <v>7198208</v>
+        <v>7198238</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -987,15 +976,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>112934773</v>
+        <v>112934772</v>
       </c>
       <c r="B5" t="n">
-        <v>89913</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1003,21 +987,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5447</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1027,10 +1011,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>776809</v>
+        <v>776794</v>
       </c>
       <c r="R5" t="n">
-        <v>7198215</v>
+        <v>7198208</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,6 +1047,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2023-07-27</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1089,39 +1078,30 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>112934771</v>
+        <v>111659789</v>
       </c>
       <c r="B6" t="n">
-        <v>57281</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>99038</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>223597</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Jungfru marie nycklar</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
+          <t>Dactylorhiza maculata subsp. maculata</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr"/>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
@@ -1129,13 +1109,13 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>776770</v>
+        <v>776795</v>
       </c>
       <c r="R6" t="n">
-        <v>7198238</v>
+        <v>7198204</v>
       </c>
       <c r="S6" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T6" t="inlineStr">
         <is>
@@ -1165,11 +1145,6 @@
       <c r="AA6" t="inlineStr">
         <is>
           <t>2023-07-27</t>
-        </is>
-      </c>
-      <c r="AC6" t="inlineStr">
-        <is>
-          <t>Äldre spår</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1184,12 +1159,12 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Julia Scholten</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Linda Sandberg</t>
+          <t>Julia Scholten, Anton Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>

--- a/artfynd/A 62595-2023 artfynd.xlsx
+++ b/artfynd/A 62595-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934773</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -871,6 +881,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934656</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -973,6 +988,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934771</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1075,6 +1095,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112934772</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1168,8 +1193,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111659789</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>